--- a/ANm/Eor_Potato_results.xlsx
+++ b/ANm/Eor_Potato_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,32 +417,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>SOC Baseline (t/ha)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SOC Project (t/ha)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>SOC Difference (t/ha)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Delta SOC (t/ha)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ERs (tCO2e/ha)</t>
         </is>
@@ -481,19 +469,19 @@
         <v>2026</v>
       </c>
       <c r="B3" t="n">
-        <v>100.8652373892471</v>
+        <v>105.6381429830826</v>
       </c>
       <c r="C3" t="n">
         <v>113.9409026286368</v>
       </c>
       <c r="D3" t="n">
-        <v>13.07566523938969</v>
+        <v>8.30275964555419</v>
       </c>
       <c r="E3" t="n">
-        <v>13.07711916698707</v>
+        <v>8.304213573151571</v>
       </c>
       <c r="F3" t="n">
-        <v>47.94943694561928</v>
+        <v>30.44878310155576</v>
       </c>
     </row>
     <row r="4">
@@ -501,19 +489,19 @@
         <v>2027</v>
       </c>
       <c r="B4" t="n">
-        <v>93.45242489496913</v>
+        <v>100.9371116138929</v>
       </c>
       <c r="C4" t="n">
         <v>113.9409017419045</v>
       </c>
       <c r="D4" t="n">
-        <v>20.48847684693533</v>
+        <v>13.00379012801152</v>
       </c>
       <c r="E4" t="n">
-        <v>7.412811607545635</v>
+        <v>4.701030482457327</v>
       </c>
       <c r="F4" t="n">
-        <v>27.18030922766733</v>
+        <v>17.2371117690102</v>
       </c>
     </row>
     <row r="5">
@@ -521,19 +509,19 @@
         <v>2028</v>
       </c>
       <c r="B5" t="n">
-        <v>88.38662296983563</v>
+        <v>97.73408267606563</v>
       </c>
       <c r="C5" t="n">
         <v>113.9409009003157</v>
       </c>
       <c r="D5" t="n">
-        <v>25.55427793048005</v>
+        <v>16.20681822425006</v>
       </c>
       <c r="E5" t="n">
-        <v>5.065801083544727</v>
+        <v>3.20302809623854</v>
       </c>
       <c r="F5" t="n">
-        <v>18.57460397299733</v>
+        <v>11.74443635287465</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +529,19 @@
         <v>2029</v>
       </c>
       <c r="B6" t="n">
-        <v>84.58974720815529</v>
+        <v>95.34474481987299</v>
       </c>
       <c r="C6" t="n">
         <v>113.9409001015723</v>
       </c>
       <c r="D6" t="n">
-        <v>29.35115289341702</v>
+        <v>18.59615528169932</v>
       </c>
       <c r="E6" t="n">
-        <v>3.796874962936968</v>
+        <v>2.389337057449268</v>
       </c>
       <c r="F6" t="n">
-        <v>13.92187486410222</v>
+        <v>8.760902543980649</v>
       </c>
     </row>
     <row r="7">
@@ -561,19 +549,19 @@
         <v>2030</v>
       </c>
       <c r="B7" t="n">
-        <v>81.5027518448402</v>
+        <v>93.41380506464007</v>
       </c>
       <c r="C7" t="n">
         <v>113.940899343493</v>
       </c>
       <c r="D7" t="n">
-        <v>32.43814749865278</v>
+        <v>20.52709427885291</v>
       </c>
       <c r="E7" t="n">
-        <v>3.086994605235759</v>
+        <v>1.930938997153589</v>
       </c>
       <c r="F7" t="n">
-        <v>11.31898021919778</v>
+        <v>7.080109656229827</v>
       </c>
     </row>
     <row r="8">
@@ -581,19 +569,19 @@
         <v>2031</v>
       </c>
       <c r="B8" t="n">
-        <v>78.83211387677952</v>
+        <v>91.75435040851453</v>
       </c>
       <c r="C8" t="n">
         <v>113.9408986240075</v>
       </c>
       <c r="D8" t="n">
-        <v>35.108784747228</v>
+        <v>22.18654821549299</v>
       </c>
       <c r="E8" t="n">
-        <v>2.670637248575218</v>
+        <v>1.659453936640077</v>
       </c>
       <c r="F8" t="n">
-        <v>9.792336578109134</v>
+        <v>6.084664434346948</v>
       </c>
     </row>
     <row r="9">
@@ -601,19 +589,19 @@
         <v>2032</v>
       </c>
       <c r="B9" t="n">
-        <v>76.42208178361501</v>
+        <v>90.26689060671477</v>
       </c>
       <c r="C9" t="n">
         <v>113.9408979411511</v>
       </c>
       <c r="D9" t="n">
-        <v>37.51881615753612</v>
+        <v>23.67400733443637</v>
       </c>
       <c r="E9" t="n">
-        <v>2.410031410308122</v>
+        <v>1.487459118943377</v>
       </c>
       <c r="F9" t="n">
-        <v>8.836781837796446</v>
+        <v>5.45401676945905</v>
       </c>
     </row>
     <row r="10">
@@ -621,19 +609,19 @@
         <v>2033</v>
       </c>
       <c r="B10" t="n">
-        <v>74.18899724254516</v>
+        <v>88.8977218759328</v>
       </c>
       <c r="C10" t="n">
         <v>113.940897293059</v>
       </c>
       <c r="D10" t="n">
-        <v>39.75190005051384</v>
+        <v>25.04317541712619</v>
       </c>
       <c r="E10" t="n">
-        <v>2.233083892977717</v>
+        <v>1.369168082689825</v>
       </c>
       <c r="F10" t="n">
-        <v>8.18797427425163</v>
+        <v>5.020282969862691</v>
       </c>
     </row>
     <row r="11">
@@ -641,19 +629,19 @@
         <v>2034</v>
       </c>
       <c r="B11" t="n">
-        <v>72.08713163881205</v>
+        <v>87.61725790552983</v>
       </c>
       <c r="C11" t="n">
         <v>113.9408966779613</v>
       </c>
       <c r="D11" t="n">
-        <v>41.85376503914921</v>
+        <v>26.32363877243144</v>
       </c>
       <c r="E11" t="n">
-        <v>2.10186498863537</v>
+        <v>1.280463355305244</v>
       </c>
       <c r="F11" t="n">
-        <v>7.706838291663023</v>
+        <v>4.695032302785894</v>
       </c>
     </row>
     <row r="12">
@@ -661,19 +649,19 @@
         <v>2035</v>
       </c>
       <c r="B12" t="n">
-        <v>70.09079546749905</v>
+        <v>86.40867530870298</v>
       </c>
       <c r="C12" t="n">
         <v>113.9408960941782</v>
       </c>
       <c r="D12" t="n">
-        <v>43.85010062667916</v>
+        <v>27.53222078547523</v>
       </c>
       <c r="E12" t="n">
-        <v>1.996335587529956</v>
+        <v>1.208582013043795</v>
       </c>
       <c r="F12" t="n">
-        <v>7.319897154276504</v>
+        <v>4.431467381160583</v>
       </c>
     </row>
     <row r="13">
@@ -681,19 +669,19 @@
         <v>2036</v>
       </c>
       <c r="B13" t="n">
-        <v>68.18493276026125</v>
+        <v>85.26194003707823</v>
       </c>
       <c r="C13" t="n">
         <v>113.9408955401156</v>
       </c>
       <c r="D13" t="n">
-        <v>45.75596277985433</v>
+        <v>28.67895550303734</v>
       </c>
       <c r="E13" t="n">
-        <v>1.905862153175164</v>
+        <v>1.146734717562111</v>
       </c>
       <c r="F13" t="n">
-        <v>6.988161228308935</v>
+        <v>4.204693964394409</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +689,19 @@
         <v>2037</v>
       </c>
       <c r="B14" t="n">
-        <v>66.36016435917401</v>
+        <v>84.17065676716952</v>
       </c>
       <c r="C14" t="n">
         <v>113.9408950142603</v>
       </c>
       <c r="D14" t="n">
-        <v>47.58073065508631</v>
+        <v>29.7702382470908</v>
       </c>
       <c r="E14" t="n">
-        <v>1.824767875231984</v>
+        <v>1.091282744053458</v>
       </c>
       <c r="F14" t="n">
-        <v>6.690815542517275</v>
+        <v>4.001370061529347</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +709,19 @@
         <v>2038</v>
       </c>
       <c r="B15" t="n">
-        <v>64.61017113217098</v>
+        <v>83.13040398385489</v>
       </c>
       <c r="C15" t="n">
         <v>113.9408945151764</v>
       </c>
       <c r="D15" t="n">
-        <v>49.33072338300539</v>
+        <v>30.81049053132148</v>
       </c>
       <c r="E15" t="n">
-        <v>1.749992727919079</v>
+        <v>1.040252284230675</v>
       </c>
       <c r="F15" t="n">
-        <v>6.416640002369955</v>
+        <v>3.814258375512475</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +729,19 @@
         <v>2039</v>
       </c>
       <c r="B16" t="n">
-        <v>62.93031015038313</v>
+        <v>82.13785240485807</v>
       </c>
       <c r="C16" t="n">
         <v>113.9408940415008</v>
       </c>
       <c r="D16" t="n">
-        <v>51.01058389111767</v>
+        <v>31.80304163664273</v>
       </c>
       <c r="E16" t="n">
-        <v>1.679860508112277</v>
+        <v>0.9925511053212546</v>
       </c>
       <c r="F16" t="n">
-        <v>6.159488529745016</v>
+        <v>3.6393540528446</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +749,19 @@
         <v>2040</v>
       </c>
       <c r="B17" t="n">
-        <v>61.31688126118864</v>
+        <v>81.19029689698627</v>
       </c>
       <c r="C17" t="n">
         <v>113.9408935919401</v>
       </c>
       <c r="D17" t="n">
-        <v>52.62401233075148</v>
+        <v>32.75059669495386</v>
       </c>
       <c r="E17" t="n">
-        <v>1.613428439633815</v>
+        <v>0.9475550583111243</v>
       </c>
       <c r="F17" t="n">
-        <v>5.91590427865732</v>
+        <v>3.474368547140789</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +769,19 @@
         <v>2041</v>
       </c>
       <c r="B18" t="n">
-        <v>59.76673702156624</v>
+        <v>80.28540684059976</v>
       </c>
       <c r="C18" t="n">
         <v>113.9408931652666</v>
       </c>
       <c r="D18" t="n">
-        <v>54.17415614370037</v>
+        <v>33.65548632466684</v>
       </c>
       <c r="E18" t="n">
-        <v>1.550143812948882</v>
+        <v>0.9048896297129829</v>
       </c>
       <c r="F18" t="n">
-        <v>5.683860647479233</v>
+        <v>3.317928642280938</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +789,19 @@
         <v>2042</v>
       </c>
       <c r="B19" t="n">
-        <v>58.27707403317458</v>
+        <v>79.42109199615916</v>
       </c>
       <c r="C19" t="n">
         <v>113.940892760315</v>
       </c>
       <c r="D19" t="n">
-        <v>55.66381872714044</v>
+        <v>34.51980076415586</v>
       </c>
       <c r="E19" t="n">
-        <v>1.489662583440079</v>
+        <v>0.8643144394890214</v>
       </c>
       <c r="F19" t="n">
-        <v>5.462096139280291</v>
+        <v>3.169152944793078</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +809,19 @@
         <v>2043</v>
       </c>
       <c r="B20" t="n">
-        <v>56.8453202015711</v>
+        <v>78.59542950760907</v>
       </c>
       <c r="C20" t="n">
         <v>113.9408923759796</v>
       </c>
       <c r="D20" t="n">
-        <v>57.09557217440849</v>
+        <v>35.34546286837052</v>
       </c>
       <c r="E20" t="n">
-        <v>1.431753447268044</v>
+        <v>0.8256621042146577</v>
       </c>
       <c r="F20" t="n">
-        <v>5.249762639982826</v>
+        <v>3.027427715453745</v>
       </c>
     </row>
     <row r="21">
@@ -841,19 +829,19 @@
         <v>2044</v>
       </c>
       <c r="B21" t="n">
-        <v>55.46907278921725</v>
+        <v>77.80662332133737</v>
       </c>
       <c r="C21" t="n">
         <v>113.9408920112107</v>
       </c>
       <c r="D21" t="n">
-        <v>58.47181922199343</v>
+        <v>36.13426868987331</v>
       </c>
       <c r="E21" t="n">
-        <v>1.37624704758494</v>
+        <v>0.7888058215027911</v>
       </c>
       <c r="F21" t="n">
-        <v>5.046239174478113</v>
+        <v>2.892288012176901</v>
       </c>
     </row>
     <row r="22">
@@ -861,19 +849,19 @@
         <v>2045</v>
       </c>
       <c r="B22" t="n">
-        <v>54.14606342594057</v>
+        <v>77.05298084150158</v>
       </c>
       <c r="C22" t="n">
         <v>113.9408916650122</v>
       </c>
       <c r="D22" t="n">
-        <v>59.79482823907163</v>
+        <v>36.88791082351062</v>
       </c>
       <c r="E22" t="n">
-        <v>1.323009017078206</v>
+        <v>0.7536421336373138</v>
       </c>
       <c r="F22" t="n">
-        <v>4.85103306262009</v>
+        <v>2.763354490003484</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +869,19 @@
         <v>2046</v>
       </c>
       <c r="B23" t="n">
-        <v>52.87413748195969</v>
+        <v>76.3328987956925</v>
       </c>
       <c r="C23" t="n">
         <v>113.9408913364387</v>
       </c>
       <c r="D23" t="n">
-        <v>61.066753854479</v>
+        <v>37.6079925407462</v>
       </c>
       <c r="E23" t="n">
-        <v>1.271925615407369</v>
+        <v>0.7200817172355727</v>
       </c>
       <c r="F23" t="n">
-        <v>4.663727256493686</v>
+        <v>2.640299629863767</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +889,19 @@
         <v>2047</v>
       </c>
       <c r="B24" t="n">
-        <v>51.65124114434219</v>
+        <v>75.64485406411514</v>
       </c>
       <c r="C24" t="n">
         <v>113.9408910245929</v>
       </c>
       <c r="D24" t="n">
-        <v>62.28964988025069</v>
+        <v>38.29603696047775</v>
       </c>
       <c r="E24" t="n">
-        <v>1.222896025771689</v>
+        <v>0.6880444197315541</v>
       </c>
       <c r="F24" t="n">
-        <v>4.483952094496193</v>
+        <v>2.522829539015698</v>
       </c>
     </row>
     <row r="25">
@@ -921,19 +909,19 @@
         <v>2048</v>
       </c>
       <c r="B25" t="n">
-        <v>50.47541267260896</v>
+        <v>74.98739722250552</v>
       </c>
       <c r="C25" t="n">
         <v>113.9408907286231</v>
       </c>
       <c r="D25" t="n">
-        <v>63.46547805601418</v>
+        <v>38.95349350611762</v>
       </c>
       <c r="E25" t="n">
-        <v>1.175828175763492</v>
+        <v>0.6574565456398744</v>
       </c>
       <c r="F25" t="n">
-        <v>4.31136997779947</v>
+        <v>2.41067400067954</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +929,19 @@
         <v>2049</v>
       </c>
       <c r="B26" t="n">
-        <v>49.34477596517407</v>
+        <v>74.35914760453768</v>
       </c>
       <c r="C26" t="n">
         <v>113.9408904477213</v>
       </c>
       <c r="D26" t="n">
-        <v>64.59611448254725</v>
+        <v>39.58174284318363</v>
       </c>
       <c r="E26" t="n">
-        <v>1.130636426533066</v>
+        <v>0.6282493370660092</v>
       </c>
       <c r="F26" t="n">
-        <v>4.145666897287907</v>
+        <v>2.303580902575367</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +949,19 @@
         <v>2050</v>
       </c>
       <c r="B27" t="n">
-        <v>48.25753544335073</v>
+        <v>73.75878924757251</v>
       </c>
       <c r="C27" t="n">
         <v>113.9408901811202</v>
       </c>
       <c r="D27" t="n">
-        <v>65.68335473776943</v>
+        <v>40.18210093354766</v>
       </c>
       <c r="E27" t="n">
-        <v>1.087240255222184</v>
+        <v>0.6003580903640255</v>
       </c>
       <c r="F27" t="n">
-        <v>3.986547602481342</v>
+        <v>2.201312998001427</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +969,19 @@
         <v>2051</v>
       </c>
       <c r="B28" t="n">
-        <v>47.21197172226672</v>
+        <v>73.1850673808419</v>
       </c>
       <c r="C28" t="n">
         <v>113.9408899280917</v>
       </c>
       <c r="D28" t="n">
-        <v>66.72891820582501</v>
+        <v>40.75582254724983</v>
       </c>
       <c r="E28" t="n">
-        <v>1.045563468055576</v>
+        <v>0.5737216137021761</v>
       </c>
       <c r="F28" t="n">
-        <v>3.833732716203779</v>
+        <v>2.103645916907979</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +989,19 @@
         <v>2052</v>
       </c>
       <c r="B29" t="n">
-        <v>46.20643778279641</v>
+        <v>72.63678527149557</v>
       </c>
       <c r="C29" t="n">
         <v>113.9408896879449</v>
       </c>
       <c r="D29" t="n">
-        <v>67.73445190514855</v>
+        <v>41.30410441644938</v>
       </c>
       <c r="E29" t="n">
-        <v>1.005533699323536</v>
+        <v>0.5482818691995419</v>
       </c>
       <c r="F29" t="n">
-        <v>3.686956897519631</v>
+        <v>2.010366853731654</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1009,19 @@
         <v>2053</v>
       </c>
       <c r="B30" t="n">
-        <v>45.23935548829741</v>
+        <v>72.1128013268433</v>
       </c>
       <c r="C30" t="n">
         <v>113.9408894600241</v>
       </c>
       <c r="D30" t="n">
-        <v>68.70153397172669</v>
+        <v>41.8280881331808</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9670820665781434</v>
+        <v>0.5239837167314221</v>
       </c>
       <c r="F30" t="n">
-        <v>3.545967577453192</v>
+        <v>1.921273628015214</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1029,19 @@
         <v>2054</v>
       </c>
       <c r="B31" t="n">
-        <v>44.30921235880113</v>
+        <v>71.61202639521116</v>
       </c>
       <c r="C31" t="n">
         <v>113.9408892437067</v>
       </c>
       <c r="D31" t="n">
-        <v>69.63167688490553</v>
+        <v>42.3288628484955</v>
       </c>
       <c r="E31" t="n">
-        <v>0.930142913178841</v>
+        <v>0.5007747153147051</v>
       </c>
       <c r="F31" t="n">
-        <v>3.410524014989084</v>
+        <v>1.836173956153919</v>
       </c>
     </row>
     <row r="32">
@@ -1061,19 +1049,19 @@
         <v>2055</v>
       </c>
       <c r="B32" t="n">
-        <v>43.41455855201813</v>
+        <v>71.13342123138067</v>
       </c>
       <c r="C32" t="n">
         <v>113.9408890384019</v>
       </c>
       <c r="D32" t="n">
-        <v>70.52633048638378</v>
+        <v>42.80746780702125</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8946536014782538</v>
+        <v>0.4786049585257501</v>
       </c>
       <c r="F32" t="n">
-        <v>3.280396538753597</v>
+        <v>1.754884847927751</v>
       </c>
     </row>
     <row r="33">
@@ -1081,19 +1069,19 @@
         <v>2056</v>
       </c>
       <c r="B33" t="n">
-        <v>42.55400402022175</v>
+        <v>70.675994105257</v>
       </c>
       <c r="C33" t="n">
         <v>113.9408888435493</v>
       </c>
       <c r="D33" t="n">
-        <v>71.38688482332753</v>
+        <v>43.26489473829228</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8605543369437498</v>
+        <v>0.45742693127103</v>
       </c>
       <c r="F33" t="n">
-        <v>3.155365902127083</v>
+        <v>1.67723208132711</v>
       </c>
     </row>
     <row r="34">
@@ -1101,19 +1089,19 @@
         <v>2057</v>
       </c>
       <c r="B34" t="n">
-        <v>41.72621582276581</v>
+        <v>70.23879853933141</v>
       </c>
       <c r="C34" t="n">
         <v>113.9408886586166</v>
       </c>
       <c r="D34" t="n">
-        <v>72.21467283585083</v>
+        <v>43.70209011928523</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8277880125232997</v>
+        <v>0.4371953809929465</v>
       </c>
       <c r="F34" t="n">
-        <v>3.035222712585432</v>
+        <v>1.603049730307471</v>
       </c>
     </row>
     <row r="35">
@@ -1121,19 +1109,19 @@
         <v>2058</v>
       </c>
       <c r="B35" t="n">
-        <v>40.92991557990574</v>
+        <v>69.82093116435701</v>
       </c>
       <c r="C35" t="n">
         <v>113.9408884830989</v>
       </c>
       <c r="D35" t="n">
-        <v>73.01097290319319</v>
+        <v>44.11995731874192</v>
       </c>
       <c r="E35" t="n">
-        <v>0.7963000673423579</v>
+        <v>0.417867199456694</v>
       </c>
       <c r="F35" t="n">
-        <v>2.919766913588646</v>
+        <v>1.532179731341212</v>
       </c>
     </row>
     <row r="36">
@@ -1141,19 +1129,19 @@
         <v>2059</v>
       </c>
       <c r="B36" t="n">
-        <v>40.1638770569585</v>
+        <v>69.42152968488136</v>
       </c>
       <c r="C36" t="n">
         <v>113.9408883165168</v>
       </c>
       <c r="D36" t="n">
-        <v>73.77701125955834</v>
+        <v>44.51935863163547</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7660383563651436</v>
+        <v>0.399401312893545</v>
       </c>
       <c r="F36" t="n">
-        <v>2.808807306672193</v>
+        <v>1.464471480609665</v>
       </c>
     </row>
     <row r="37">
@@ -1161,19 +1149,19 @@
         <v>2060</v>
       </c>
       <c r="B37" t="n">
-        <v>39.42692386984058</v>
+        <v>69.03977094762723</v>
       </c>
       <c r="C37" t="n">
         <v>113.9408881584154</v>
       </c>
       <c r="D37" t="n">
-        <v>74.5139642885748</v>
+        <v>44.90111721078814</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7369530290164619</v>
+        <v>0.3817585791526739</v>
       </c>
       <c r="F37" t="n">
-        <v>2.702161106393694</v>
+        <v>1.399781456893137</v>
       </c>
     </row>
     <row r="38">
@@ -1181,19 +1169,19 @@
         <v>2061</v>
       </c>
       <c r="B38" t="n">
-        <v>38.71792730428974</v>
+        <v>68.67486910658432</v>
       </c>
       <c r="C38" t="n">
         <v>113.9408880083629</v>
       </c>
       <c r="D38" t="n">
-        <v>75.22296070407316</v>
+        <v>45.26601890177858</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7089964154983619</v>
+        <v>0.3649016909904361</v>
       </c>
       <c r="F38" t="n">
-        <v>2.599653523493993</v>
+        <v>1.337972866964932</v>
       </c>
     </row>
     <row r="39">
@@ -1201,19 +1189,19 @@
         <v>2062</v>
       </c>
       <c r="B39" t="n">
-        <v>38.03580424193729</v>
+        <v>68.32607387928485</v>
       </c>
       <c r="C39" t="n">
         <v>113.9408878659496</v>
       </c>
       <c r="D39" t="n">
-        <v>75.90508362401235</v>
+        <v>45.61481398666479</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6821229199391894</v>
+        <v>0.3487950848862056</v>
       </c>
       <c r="F39" t="n">
-        <v>2.501117373110361</v>
+        <v>1.27891531124942</v>
       </c>
     </row>
     <row r="40">
@@ -1221,19 +1209,19 @@
         <v>2063</v>
       </c>
       <c r="B40" t="n">
-        <v>37.37951518703191</v>
+        <v>67.99266888919706</v>
       </c>
       <c r="C40" t="n">
         <v>113.9408877307867</v>
       </c>
       <c r="D40" t="n">
-        <v>76.56137254375474</v>
+        <v>45.94821884158959</v>
       </c>
       <c r="E40" t="n">
-        <v>0.6562889197423942</v>
+        <v>0.3334048549248081</v>
       </c>
       <c r="F40" t="n">
-        <v>2.406392705722112</v>
+        <v>1.22248446805763</v>
       </c>
     </row>
     <row r="41">
@@ -1241,19 +1229,19 @@
         <v>2064</v>
       </c>
       <c r="B41" t="n">
-        <v>36.74806238811527</v>
+        <v>67.67397008954231</v>
       </c>
       <c r="C41" t="n">
         <v>113.9408876025048</v>
       </c>
       <c r="D41" t="n">
-        <v>77.19282521438954</v>
+        <v>46.26691751296251</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6314526706348005</v>
+        <v>0.3186986713729141</v>
       </c>
       <c r="F41" t="n">
-        <v>2.315326458994269</v>
+        <v>1.168561795034018</v>
       </c>
     </row>
     <row r="42">
@@ -1261,19 +1249,19 @@
         <v>2065</v>
       </c>
       <c r="B42" t="n">
-        <v>36.1404880493678</v>
+        <v>67.36932426415875</v>
       </c>
       <c r="C42" t="n">
         <v>113.9408874807538</v>
       </c>
       <c r="D42" t="n">
-        <v>77.80039943138598</v>
+        <v>46.57156321659504</v>
       </c>
       <c r="E42" t="n">
-        <v>0.60757421699644</v>
+        <v>0.3046457036325307</v>
       </c>
       <c r="F42" t="n">
-        <v>2.227772128986947</v>
+        <v>1.117034246652613</v>
       </c>
     </row>
   </sheetData>
